--- a/server/lookup_tables/codigos modelos nissan.xlsx
+++ b/server/lookup_tables/codigos modelos nissan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marlen Virga\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marlen Virga\Desktop\gabi actis\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="67">
   <si>
     <t>Código</t>
   </si>
@@ -32,242 +32,206 @@
     <t>Modelo</t>
   </si>
   <si>
-    <t>BDTALEFN18ELB—F-</t>
-  </si>
-  <si>
-    <t>VERSA 1.6 SENSE MT</t>
-  </si>
-  <si>
-    <t>BDTALGFN18ELB—F-</t>
-  </si>
-  <si>
     <t>VERSA 1.6 ADVANCE MT</t>
   </si>
   <si>
-    <t>BDTALGZN18ELB—F-</t>
-  </si>
-  <si>
     <t>VERSA 1.6 ADVANCE CVT</t>
   </si>
   <si>
-    <t>BDTALGZN18ELB—DFS</t>
-  </si>
-  <si>
-    <t>VERSA 1.6 SR CVT</t>
-  </si>
-  <si>
-    <t>BDTALIZN18ELB—F-</t>
-  </si>
-  <si>
     <t>VERSA 1.6 EXCLUSIVE CVT</t>
   </si>
   <si>
-    <t>BDRALDZB18DLA——</t>
-  </si>
-  <si>
     <t>SENTRA 2.0 ADVANCE CVT</t>
   </si>
   <si>
-    <t>BDRALRZB18DLA——</t>
-  </si>
-  <si>
     <t>SENTRA 2.0 SR CVT</t>
   </si>
   <si>
-    <t>BDRALRZB18DLAC——</t>
-  </si>
-  <si>
     <t>SENTRA 2.0 SR CVT NIGHTFALL</t>
   </si>
   <si>
-    <t>BDRALJZB18DLA——</t>
-  </si>
-  <si>
     <t>SENTRA 2.0 EXCLUSIVE CVT</t>
   </si>
   <si>
-    <t>FDTALRFP15ELA—AA-</t>
-  </si>
-  <si>
-    <t>KICKS PLAY 1.6 SENSE MT</t>
-  </si>
-  <si>
-    <t>FDTALSZP15ELA—AB-</t>
-  </si>
-  <si>
-    <t>KICKS PLAY 1.6 ADVANCE CVT</t>
-  </si>
-  <si>
-    <t>FDTALSZP15ELA—AC-</t>
-  </si>
-  <si>
     <t>KICKS PLAY 1.6 ADVANCE CVT PLUS</t>
   </si>
   <si>
-    <t>FDTALVZP15ELA—B—</t>
-  </si>
-  <si>
     <t>KICKS PLAY 1.6 EXCLUSIVE CVT</t>
   </si>
   <si>
-    <t>FDTALCZP15ELA-B—A</t>
-  </si>
-  <si>
     <t>KAIT 1.6 SENSE CVT</t>
   </si>
   <si>
-    <t>FDTALDZP15ELA-BA-A</t>
-  </si>
-  <si>
     <t>KAIT 1.6 ADVANCE CVT</t>
   </si>
   <si>
-    <t>FDTALGZP15ELA—A-A</t>
-  </si>
-  <si>
     <t>KAIT 1.6 EXCLUSIVE CVT</t>
   </si>
   <si>
-    <t>FRNALB3P16ELA——A</t>
-  </si>
-  <si>
     <t>KICKS SENSE DCT 1.0T</t>
   </si>
   <si>
-    <t>FRNALD3P16ELA——A</t>
-  </si>
-  <si>
     <t>KICKS ADVANCE DCT 1.0T</t>
   </si>
   <si>
-    <t>FRNALG3P16ELAA—A</t>
-  </si>
-  <si>
     <t>KICKS EXCLUSIVE DCT 1.0T</t>
   </si>
   <si>
-    <t>CTSALEYD23FRP-FSGH</t>
-  </si>
-  <si>
     <t>FRONTIER S 4X2 MT 2.3 D CD</t>
   </si>
   <si>
-    <t>CTSALELD23IRP-FSGH</t>
-  </si>
-  <si>
     <t>FRONTIER S 4X2 AT 2.3 D CD</t>
   </si>
   <si>
-    <t>CTSNLEYD23FRP-FSGH</t>
-  </si>
-  <si>
     <t>FRONTIER S 4X4 MT 2.3 D CD</t>
   </si>
   <si>
-    <t>CTSALTYD23FRP—SGH</t>
-  </si>
-  <si>
     <t>FRONTIER XE 4X2 MT 2.3 D CD</t>
   </si>
   <si>
-    <t>CTSALTLD23IRP—SGH</t>
-  </si>
-  <si>
     <t>FRONTIER XE 4X2 AT 2.3 D CD</t>
   </si>
   <si>
-    <t>CTSNLMLD23IRP—SKH</t>
-  </si>
-  <si>
     <t>FRONTIER X-GEAR 4X4 AT 2.3 D CD</t>
   </si>
   <si>
-    <t>CTSNLTYD23IRP—SGH</t>
-  </si>
-  <si>
     <t>FRONTIER XE 4X4 MT 2.3 D CD</t>
   </si>
   <si>
-    <t>CTSALWLD23IRP—BM-</t>
-  </si>
-  <si>
     <t>FRONTIER PLATINUM 4X2 AT 2.3 D CD</t>
   </si>
   <si>
-    <t>CTSNLWLD23IRP—BQH</t>
-  </si>
-  <si>
     <t>FRONTIER PLATINUM 4X4 AT 2.3 D CD</t>
   </si>
   <si>
-    <t>CTSNLYLD23IRP—SR-</t>
-  </si>
-  <si>
     <t>FRONTIER PRO4X 4X4 AT 2.3 D CD</t>
   </si>
   <si>
-    <t>JCJALDWT33ELAC-A-A</t>
-  </si>
-  <si>
     <t>X-TRAIL 2.5 ADVANCE CVT</t>
   </si>
   <si>
-    <t>JCJNLGWT33ELAF-ACA</t>
-  </si>
-  <si>
     <t>X-TRAIL 2.5 EXCLUSIVE CVT</t>
   </si>
   <si>
-    <t>JDNNLG9T33TLAF-ACA</t>
-  </si>
-  <si>
-    <t>X-TRAIL EPOWER EXCLUSIVE CVT</t>
-  </si>
-  <si>
     <t xml:space="preserve">                                                                                                                                                                                                        *</t>
   </si>
   <si>
-    <t>CIVIC HEV E CVT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIVIC FE4 HEV </t>
-  </si>
-  <si>
-    <t>CRV HEV E CVT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CR-V HYBRID RS6 HEV </t>
-  </si>
-  <si>
-    <t>CRV EXL AWD CVT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRV EXL AWD CVT </t>
-  </si>
-  <si>
-    <t>HRVEXL2WDCVT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HR-V EXL 2WD CVT </t>
-  </si>
-  <si>
-    <t>WRVEXL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WR-V DG5 39K EXL </t>
-  </si>
-  <si>
-    <t>ZRVTOURING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZR-V RZ1 TRG </t>
+    <t xml:space="preserve">VERSA 1.6 SENSE MT </t>
+  </si>
+  <si>
+    <t>BDTALEFN18ELBF-</t>
+  </si>
+  <si>
+    <t>BDTALGFN18ELB-F</t>
+  </si>
+  <si>
+    <t>BDTALGZN18ELB-F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERSA 1.6 SR CVT </t>
+  </si>
+  <si>
+    <t>BDTALGZN18ELBDF</t>
+  </si>
+  <si>
+    <t>BDTALIZN18ELB-F</t>
+  </si>
+  <si>
+    <t>BDRALDZB18DLA-</t>
+  </si>
+  <si>
+    <t>BDRALRZB18DLA-</t>
+  </si>
+  <si>
+    <t>BDRALRZB18DLAC-</t>
+  </si>
+  <si>
+    <t>BDRALJZB18DLA-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KICKS PLAY 1.6 SENSE MT </t>
+  </si>
+  <si>
+    <t>FDTALRFP15ELA-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KICKS PLAY 1.6 ADVANCE CVT </t>
+  </si>
+  <si>
+    <t>FDTALSZP15ELA-B</t>
+  </si>
+  <si>
+    <t>FDTALSZP15ELA-A</t>
+  </si>
+  <si>
+    <t>FDTALVZP15ELA-B</t>
+  </si>
+  <si>
+    <t>FDTALCZP15ELA-B</t>
+  </si>
+  <si>
+    <t>FDTALDZP15ELA-B</t>
+  </si>
+  <si>
+    <t>FDTALGZP15ELA-A</t>
+  </si>
+  <si>
+    <t>FRNALB3P16ELA-A</t>
+  </si>
+  <si>
+    <t>FRNALD3P16ELA-A</t>
+  </si>
+  <si>
+    <t>FRNALG3P16ELA-A</t>
+  </si>
+  <si>
+    <t>CTSALEYD23FRP-F</t>
+  </si>
+  <si>
+    <t>CTSALELD23IRP-F</t>
+  </si>
+  <si>
+    <t>CTSNLEYD23FRP-F</t>
+  </si>
+  <si>
+    <t>CTSALTYD23FRP-S</t>
+  </si>
+  <si>
+    <t>CTSALTLD23IRP-S</t>
+  </si>
+  <si>
+    <t>CTSNLMLD23IRP-S</t>
+  </si>
+  <si>
+    <t>CTSNLTYD23IRP-S</t>
+  </si>
+  <si>
+    <t>CTSALWLD23IRP-B</t>
+  </si>
+  <si>
+    <t>CTS NLWLD23IRP-</t>
+  </si>
+  <si>
+    <t>CTSNLYLD23IRP-S</t>
+  </si>
+  <si>
+    <t>JCJALDWT33ELAC-</t>
+  </si>
+  <si>
+    <t>JCJNLGWT33ELAF</t>
+  </si>
+  <si>
+    <t>X-TRAIL 2.5 EPOWER EXCLUSIVE CVT</t>
+  </si>
+  <si>
+    <t>JDNNLG9T33TLAF-</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -283,6 +247,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -292,7 +264,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -300,19 +272,133 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -593,338 +679,316 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.44140625" customWidth="1"/>
+    <col min="1" max="1" width="38.44140625" customWidth="1"/>
     <col min="2" max="2" width="27.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:2" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B10" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B13" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B14" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="B15" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B16" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="B17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="10"/>
+    </row>
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B18" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="B19" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B20" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="B21" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B22" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="B23" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B24" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="B25" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B26" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="B27" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B28" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B29" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B30" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="B31" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B32" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36" spans="1:2" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B40" s="3"/>
+      <c r="B40" s="2"/>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B41" s="3"/>
+      <c r="A41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>